--- a/data/launch/adoption-measures-draft.xlsx
+++ b/data/launch/adoption-measures-draft.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Count of accounts with Assist switched on</t>
+          <t>Count of accounts with the help portal switched on</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -506,12 +506,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Proposals created</t>
+          <t>Suggestions created</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Count of proposals in the period</t>
+          <t>Count of suggestions in the period</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deflection rate</t>
+          <t>Self-service rate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Proposals requiring human review, per engineer per week</t>
+          <t>Suggestions requiring human review, per engineer per week</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
